--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="DealerFunction" sheetId="5" r:id="rId1"/>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>荷官描述多语言</t>
     </r>
     <r>
@@ -119,7 +125,7 @@
     <t>describe</t>
   </si>
   <si>
-    <t>1030001_100</t>
+    <t>1980000_100</t>
   </si>
 </sst>
 </file>
@@ -297,12 +303,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1198,8 +1204,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <f>300000+A5</f>
-        <v>320001</v>
+        <v>47036</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -1212,8 +1217,7 @@
         <v>11001</v>
       </c>
       <c r="G5" s="1">
-        <f>400000+A5</f>
-        <v>420001</v>
+        <v>47037</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1225,8 +1229,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <f>300000+A6</f>
-        <v>320002</v>
+        <v>47038</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -1239,8 +1242,7 @@
         <v>11002</v>
       </c>
       <c r="G6" s="1">
-        <f>400000+A6</f>
-        <v>420002</v>
+        <v>47039</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1252,8 +1254,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <f>300000+A7</f>
-        <v>320003</v>
+        <v>47040</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -1266,8 +1267,7 @@
         <v>11003</v>
       </c>
       <c r="G7" s="1">
-        <f>400000+A7</f>
-        <v>420003</v>
+        <v>47041</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>荷官名字多语言ID</t>
+  </si>
+  <si>
+    <t>图片资源名</t>
   </si>
   <si>
     <t>聘请费用</t>
@@ -104,6 +107,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>hiringExpenses</t>
   </si>
   <si>
@@ -125,7 +134,19 @@
     <t>describe</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>wddc_paizuo_1.png</t>
+  </si>
+  <si>
     <t>1980000_100</t>
+  </si>
+  <si>
+    <t>wddc_paizuo_2.png</t>
+  </si>
+  <si>
+    <t>wddc_zhaunpan.png</t>
   </si>
 </sst>
 </file>
@@ -508,12 +529,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -640,7 +676,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -652,34 +688,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -764,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -772,6 +808,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1116,17 +1155,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15.125" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="4" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:7">
+    <row r="1" ht="15" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1145,57 +1184,74 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="4" spans="4:8">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <f>20000+B5</f>
         <v>20001</v>
@@ -1207,20 +1263,23 @@
         <v>47036</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <f>2*60*60</f>
         <v>7200</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>11001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>47037</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <f>20000+B6</f>
         <v>20002</v>
@@ -1232,20 +1291,23 @@
         <v>47038</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
         <f>4*60*60</f>
         <v>14400</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>11002</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>47039</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <f>20000+B7</f>
         <v>20003</v>
@@ -1257,16 +1319,19 @@
         <v>47040</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
         <f>8*60*60</f>
         <v>28800</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>11003</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>47041</v>
       </c>
     </row>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -137,16 +137,16 @@
     <t>client</t>
   </si>
   <si>
-    <t>wddc_paizuo_1.png</t>
+    <t>wddc_gzry_3.png</t>
   </si>
   <si>
     <t>1980000_100</t>
   </si>
   <si>
-    <t>wddc_paizuo_2.png</t>
-  </si>
-  <si>
-    <t>wddc_zhaunpan.png</t>
+    <t>wddc_gzry_2.png</t>
+  </si>
+  <si>
+    <t>wddc_gzry_1.png</t>
   </si>
 </sst>
 </file>
@@ -324,12 +324,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="DealerFunction" sheetId="5" r:id="rId1"/>
@@ -56,12 +56,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+平均每分钟产出金币
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -140,13 +163,19 @@
     <t>wddc_gzry_3.png</t>
   </si>
   <si>
-    <t>1980000_100</t>
+    <t>1980000_1</t>
   </si>
   <si>
     <t>wddc_gzry_2.png</t>
   </si>
   <si>
+    <t>1980000_5</t>
+  </si>
+  <si>
     <t>wddc_gzry_1.png</t>
+  </si>
+  <si>
+    <t>1980000_15</t>
   </si>
 </sst>
 </file>
@@ -1155,8 +1184,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="3" max="3" width="12.75" customWidth="1"/>
     <col min="4" max="5" width="14.75" customWidth="1"/>
@@ -1165,7 +1194,7 @@
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:8">
+    <row r="1" ht="15" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +1220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1217,7 +1246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="4:8">
+    <row r="4" spans="1:14">
       <c r="D4" t="s">
         <v>18</v>
       </c>
@@ -1251,7 +1280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:14">
       <c r="A5">
         <f>20000+B5</f>
         <v>20001</v>
@@ -1278,8 +1307,30 @@
       <c r="H5" s="1">
         <v>47037</v>
       </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5">
+        <v>350</v>
+      </c>
+      <c r="K5">
+        <f>F5/60</f>
+        <v>120</v>
+      </c>
+      <c r="L5">
+        <f>K5*J5*I5/10000</f>
+        <v>2100</v>
+      </c>
+      <c r="M5">
+        <f>100000/100</f>
+        <v>1000</v>
+      </c>
+      <c r="N5">
+        <f>L5/M5*0.5</f>
+        <v>1.05</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:14">
       <c r="A6">
         <f>20000+B6</f>
         <v>20002</v>
@@ -1294,7 +1345,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <f>4*60*60</f>
@@ -1306,8 +1357,30 @@
       <c r="H6" s="1">
         <v>47039</v>
       </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>350</v>
+      </c>
+      <c r="K6">
+        <f>F6/60</f>
+        <v>240</v>
+      </c>
+      <c r="L6">
+        <f>K6*J6*I6/10000</f>
+        <v>8400</v>
+      </c>
+      <c r="M6">
+        <f>100000/100</f>
+        <v>1000</v>
+      </c>
+      <c r="N6">
+        <f>L6/M6*0.5</f>
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:14">
       <c r="A7">
         <f>20000+B7</f>
         <v>20003</v>
@@ -1319,10 +1392,10 @@
         <v>47040</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <f>8*60*60</f>
@@ -1333,6 +1406,28 @@
       </c>
       <c r="H7" s="1">
         <v>47041</v>
+      </c>
+      <c r="I7">
+        <v>1500</v>
+      </c>
+      <c r="J7">
+        <v>350</v>
+      </c>
+      <c r="K7">
+        <f>F7/60</f>
+        <v>480</v>
+      </c>
+      <c r="L7">
+        <f>K7*J7*I7/10000</f>
+        <v>25200</v>
+      </c>
+      <c r="M7">
+        <f>100000/100</f>
+        <v>1000</v>
+      </c>
+      <c r="N7">
+        <f>L7/M7*0.5</f>
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="DealerFunction" sheetId="5" r:id="rId1"/>
@@ -1302,7 +1302,7 @@
         <v>7200</v>
       </c>
       <c r="G5">
-        <v>11001</v>
+        <v>11002</v>
       </c>
       <c r="H5" s="1">
         <v>47037</v>
@@ -1352,7 +1352,7 @@
         <v>14400</v>
       </c>
       <c r="G6">
-        <v>11002</v>
+        <v>11004</v>
       </c>
       <c r="H6" s="1">
         <v>47039</v>
@@ -1402,7 +1402,7 @@
         <v>28800</v>
       </c>
       <c r="G7">
-        <v>11003</v>
+        <v>11006</v>
       </c>
       <c r="H7" s="1">
         <v>47041</v>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="DealerFunction" sheetId="5" r:id="rId1"/>
@@ -163,19 +163,19 @@
     <t>wddc_gzry_3.png</t>
   </si>
   <si>
-    <t>1980000_1</t>
+    <t>1980000_600</t>
   </si>
   <si>
     <t>wddc_gzry_2.png</t>
   </si>
   <si>
-    <t>1980000_5</t>
+    <t>1980000_2400</t>
   </si>
   <si>
     <t>wddc_gzry_1.png</t>
   </si>
   <si>
-    <t>1980000_15</t>
+    <t>1980000_7200</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/DealerFunction.xlsx
+++ b/hall/resources/sample/DealerFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="DealerFunction" sheetId="5" r:id="rId1"/>
@@ -163,19 +163,19 @@
     <t>wddc_gzry_3.png</t>
   </si>
   <si>
-    <t>1980000_600</t>
+    <t>1980000_1</t>
   </si>
   <si>
     <t>wddc_gzry_2.png</t>
   </si>
   <si>
-    <t>1980000_2400</t>
+    <t>1980000_5</t>
   </si>
   <si>
     <t>wddc_gzry_1.png</t>
   </si>
   <si>
-    <t>1980000_7200</t>
+    <t>1980000_15</t>
   </si>
 </sst>
 </file>
